--- a/data/solution_finder_dataset.xlsx
+++ b/data/solution_finder_dataset.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="125">
   <si>
     <t>skin_conditions</t>
   </si>
@@ -142,9 +142,6 @@
     <t>Cetaphil Daily Hydrating Lotion</t>
   </si>
   <si>
-    <t>La RochePosay Toleriane Double Repair Face Moisturizer</t>
-  </si>
-  <si>
     <t>Drunk Elephant A Passioni Retinol Cream</t>
   </si>
   <si>
@@ -188,9 +185,6 @@
   </si>
   <si>
     <t>Anti Acne Facial Mask Powder by IK Organics</t>
-  </si>
-  <si>
-    <t>EltaMD UV Clear Broad-Spectrum SPF 46</t>
   </si>
   <si>
     <t>Pure Dark Spot Remover</t>
@@ -1066,7 +1060,7 @@
         <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>34</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1080,7 +1074,7 @@
         <v>17</v>
       </c>
       <c r="D17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1094,7 +1088,7 @@
         <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1108,7 +1102,7 @@
         <v>19</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1122,7 +1116,7 @@
         <v>20</v>
       </c>
       <c r="D20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1136,7 +1130,7 @@
         <v>21</v>
       </c>
       <c r="D21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1150,7 +1144,7 @@
         <v>17</v>
       </c>
       <c r="D22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1164,7 +1158,7 @@
         <v>18</v>
       </c>
       <c r="D23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1192,7 +1186,7 @@
         <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1206,7 +1200,7 @@
         <v>21</v>
       </c>
       <c r="D26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1220,7 +1214,7 @@
         <v>17</v>
       </c>
       <c r="D27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1234,7 +1228,7 @@
         <v>18</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1248,7 +1242,7 @@
         <v>19</v>
       </c>
       <c r="D29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1262,7 +1256,7 @@
         <v>20</v>
       </c>
       <c r="D30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1276,7 +1270,7 @@
         <v>21</v>
       </c>
       <c r="D31" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1290,7 +1284,7 @@
         <v>17</v>
       </c>
       <c r="D32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1304,7 +1298,7 @@
         <v>18</v>
       </c>
       <c r="D33" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1318,7 +1312,7 @@
         <v>19</v>
       </c>
       <c r="D34" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1332,7 +1326,7 @@
         <v>20</v>
       </c>
       <c r="D35" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1346,7 +1340,7 @@
         <v>21</v>
       </c>
       <c r="D36" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1360,7 +1354,7 @@
         <v>17</v>
       </c>
       <c r="D37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1374,7 +1368,7 @@
         <v>18</v>
       </c>
       <c r="D38" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1388,7 +1382,7 @@
         <v>19</v>
       </c>
       <c r="D39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1402,7 +1396,7 @@
         <v>20</v>
       </c>
       <c r="D40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1416,7 +1410,7 @@
         <v>21</v>
       </c>
       <c r="D41" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1430,7 +1424,7 @@
         <v>17</v>
       </c>
       <c r="D42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1444,7 +1438,7 @@
         <v>18</v>
       </c>
       <c r="D43" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1458,7 +1452,7 @@
         <v>19</v>
       </c>
       <c r="D44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1472,7 +1466,7 @@
         <v>20</v>
       </c>
       <c r="D45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1486,7 +1480,7 @@
         <v>21</v>
       </c>
       <c r="D46" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1500,7 +1494,7 @@
         <v>17</v>
       </c>
       <c r="D47" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1514,7 +1508,7 @@
         <v>18</v>
       </c>
       <c r="D48" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1528,7 +1522,7 @@
         <v>19</v>
       </c>
       <c r="D49" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1542,7 +1536,7 @@
         <v>20</v>
       </c>
       <c r="D50" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1556,7 +1550,7 @@
         <v>21</v>
       </c>
       <c r="D51" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1570,7 +1564,7 @@
         <v>17</v>
       </c>
       <c r="D52" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1584,7 +1578,7 @@
         <v>18</v>
       </c>
       <c r="D53" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1598,7 +1592,7 @@
         <v>19</v>
       </c>
       <c r="D54" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1612,7 +1606,7 @@
         <v>20</v>
       </c>
       <c r="D55" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1626,7 +1620,7 @@
         <v>21</v>
       </c>
       <c r="D56" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1640,7 +1634,7 @@
         <v>17</v>
       </c>
       <c r="D57" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1654,7 +1648,7 @@
         <v>18</v>
       </c>
       <c r="D58" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1668,7 +1662,7 @@
         <v>19</v>
       </c>
       <c r="D59" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1682,7 +1676,7 @@
         <v>20</v>
       </c>
       <c r="D60" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1696,7 +1690,7 @@
         <v>21</v>
       </c>
       <c r="D61" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1710,7 +1704,7 @@
         <v>17</v>
       </c>
       <c r="D62" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1724,7 +1718,7 @@
         <v>18</v>
       </c>
       <c r="D63" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1738,7 +1732,7 @@
         <v>19</v>
       </c>
       <c r="D64" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1752,7 +1746,7 @@
         <v>20</v>
       </c>
       <c r="D65" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1766,7 +1760,7 @@
         <v>21</v>
       </c>
       <c r="D66" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1780,7 +1774,7 @@
         <v>17</v>
       </c>
       <c r="D67" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1794,7 +1788,7 @@
         <v>18</v>
       </c>
       <c r="D68" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1808,7 +1802,7 @@
         <v>19</v>
       </c>
       <c r="D69" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1822,7 +1816,7 @@
         <v>20</v>
       </c>
       <c r="D70" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1836,7 +1830,7 @@
         <v>21</v>
       </c>
       <c r="D71" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1850,7 +1844,7 @@
         <v>17</v>
       </c>
       <c r="D72" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1864,7 +1858,7 @@
         <v>18</v>
       </c>
       <c r="D73" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1878,7 +1872,7 @@
         <v>19</v>
       </c>
       <c r="D74" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -1892,7 +1886,7 @@
         <v>20</v>
       </c>
       <c r="D75" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1906,7 +1900,7 @@
         <v>21</v>
       </c>
       <c r="D76" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -1920,7 +1914,7 @@
         <v>17</v>
       </c>
       <c r="D77" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1934,7 +1928,7 @@
         <v>18</v>
       </c>
       <c r="D78" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1948,7 +1942,7 @@
         <v>19</v>
       </c>
       <c r="D79" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -1962,7 +1956,7 @@
         <v>20</v>
       </c>
       <c r="D80" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -1990,7 +1984,7 @@
         <v>17</v>
       </c>
       <c r="D82" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2004,7 +1998,7 @@
         <v>18</v>
       </c>
       <c r="D83" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2018,7 +2012,7 @@
         <v>19</v>
       </c>
       <c r="D84" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2032,7 +2026,7 @@
         <v>20</v>
       </c>
       <c r="D85" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2046,7 +2040,7 @@
         <v>21</v>
       </c>
       <c r="D86" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2060,7 +2054,7 @@
         <v>17</v>
       </c>
       <c r="D87" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2074,7 +2068,7 @@
         <v>18</v>
       </c>
       <c r="D88" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2102,7 +2096,7 @@
         <v>20</v>
       </c>
       <c r="D90" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2116,7 +2110,7 @@
         <v>21</v>
       </c>
       <c r="D91" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2130,7 +2124,7 @@
         <v>17</v>
       </c>
       <c r="D92" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2144,7 +2138,7 @@
         <v>18</v>
       </c>
       <c r="D93" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2158,7 +2152,7 @@
         <v>19</v>
       </c>
       <c r="D94" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2172,7 +2166,7 @@
         <v>20</v>
       </c>
       <c r="D95" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2186,7 +2180,7 @@
         <v>21</v>
       </c>
       <c r="D96" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2200,7 +2194,7 @@
         <v>17</v>
       </c>
       <c r="D97" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2214,7 +2208,7 @@
         <v>18</v>
       </c>
       <c r="D98" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2228,7 +2222,7 @@
         <v>19</v>
       </c>
       <c r="D99" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2242,7 +2236,7 @@
         <v>20</v>
       </c>
       <c r="D100" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2256,7 +2250,7 @@
         <v>21</v>
       </c>
       <c r="D101" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2270,7 +2264,7 @@
         <v>17</v>
       </c>
       <c r="D102" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2284,7 +2278,7 @@
         <v>18</v>
       </c>
       <c r="D103" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2298,7 +2292,7 @@
         <v>19</v>
       </c>
       <c r="D104" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2312,7 +2306,7 @@
         <v>20</v>
       </c>
       <c r="D105" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="15">
@@ -2326,7 +2320,7 @@
         <v>21</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2340,7 +2334,7 @@
         <v>17</v>
       </c>
       <c r="D107" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2354,7 +2348,7 @@
         <v>18</v>
       </c>
       <c r="D108" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2368,7 +2362,7 @@
         <v>19</v>
       </c>
       <c r="D109" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2382,7 +2376,7 @@
         <v>20</v>
       </c>
       <c r="D110" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2396,7 +2390,7 @@
         <v>21</v>
       </c>
       <c r="D111" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2410,7 +2404,7 @@
         <v>17</v>
       </c>
       <c r="D112" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2424,7 +2418,7 @@
         <v>18</v>
       </c>
       <c r="D113" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2438,7 +2432,7 @@
         <v>19</v>
       </c>
       <c r="D114" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2452,7 +2446,7 @@
         <v>20</v>
       </c>
       <c r="D115" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2466,7 +2460,7 @@
         <v>21</v>
       </c>
       <c r="D116" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2480,7 +2474,7 @@
         <v>17</v>
       </c>
       <c r="D117" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2494,7 +2488,7 @@
         <v>18</v>
       </c>
       <c r="D118" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2508,7 +2502,7 @@
         <v>19</v>
       </c>
       <c r="D119" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2522,7 +2516,7 @@
         <v>20</v>
       </c>
       <c r="D120" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2536,7 +2530,7 @@
         <v>21</v>
       </c>
       <c r="D121" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2550,7 +2544,7 @@
         <v>17</v>
       </c>
       <c r="D122" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2564,7 +2558,7 @@
         <v>18</v>
       </c>
       <c r="D123" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2578,7 +2572,7 @@
         <v>19</v>
       </c>
       <c r="D124" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2592,7 +2586,7 @@
         <v>20</v>
       </c>
       <c r="D125" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2606,7 +2600,7 @@
         <v>21</v>
       </c>
       <c r="D126" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2620,7 +2614,7 @@
         <v>17</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2634,7 +2628,7 @@
         <v>18</v>
       </c>
       <c r="D128" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2648,7 +2642,7 @@
         <v>19</v>
       </c>
       <c r="D129" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2662,7 +2656,7 @@
         <v>20</v>
       </c>
       <c r="D130" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2676,7 +2670,7 @@
         <v>21</v>
       </c>
       <c r="D131" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2690,7 +2684,7 @@
         <v>17</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2704,7 +2698,7 @@
         <v>18</v>
       </c>
       <c r="D133" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2718,7 +2712,7 @@
         <v>19</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2732,7 +2726,7 @@
         <v>20</v>
       </c>
       <c r="D135" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2746,7 +2740,7 @@
         <v>21</v>
       </c>
       <c r="D136" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -2760,7 +2754,7 @@
         <v>17</v>
       </c>
       <c r="D137" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -2774,7 +2768,7 @@
         <v>18</v>
       </c>
       <c r="D138" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -2788,7 +2782,7 @@
         <v>19</v>
       </c>
       <c r="D139" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -2802,7 +2796,7 @@
         <v>20</v>
       </c>
       <c r="D140" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -2816,7 +2810,7 @@
         <v>21</v>
       </c>
       <c r="D141" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -2830,7 +2824,7 @@
         <v>17</v>
       </c>
       <c r="D142" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -2844,7 +2838,7 @@
         <v>18</v>
       </c>
       <c r="D143" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -2858,7 +2852,7 @@
         <v>19</v>
       </c>
       <c r="D144" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -2872,7 +2866,7 @@
         <v>20</v>
       </c>
       <c r="D145" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -2886,7 +2880,7 @@
         <v>21</v>
       </c>
       <c r="D146" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -2900,7 +2894,7 @@
         <v>17</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -2914,7 +2908,7 @@
         <v>18</v>
       </c>
       <c r="D148" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -2928,7 +2922,7 @@
         <v>19</v>
       </c>
       <c r="D149" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -2942,7 +2936,7 @@
         <v>20</v>
       </c>
       <c r="D150" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -2956,7 +2950,7 @@
         <v>21</v>
       </c>
       <c r="D151" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -2970,7 +2964,7 @@
         <v>17</v>
       </c>
       <c r="D152" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -2984,7 +2978,7 @@
         <v>18</v>
       </c>
       <c r="D153" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -2998,7 +2992,7 @@
         <v>19</v>
       </c>
       <c r="D154" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3012,7 +3006,7 @@
         <v>20</v>
       </c>
       <c r="D155" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3026,7 +3020,7 @@
         <v>21</v>
       </c>
       <c r="D156" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3040,7 +3034,7 @@
         <v>17</v>
       </c>
       <c r="D157" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3054,7 +3048,7 @@
         <v>18</v>
       </c>
       <c r="D158" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3068,7 +3062,7 @@
         <v>19</v>
       </c>
       <c r="D159" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3082,7 +3076,7 @@
         <v>20</v>
       </c>
       <c r="D160" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3096,7 +3090,7 @@
         <v>21</v>
       </c>
       <c r="D161" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3110,7 +3104,7 @@
         <v>17</v>
       </c>
       <c r="D162" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3124,7 +3118,7 @@
         <v>18</v>
       </c>
       <c r="D163" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3138,7 +3132,7 @@
         <v>19</v>
       </c>
       <c r="D164" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3152,7 +3146,7 @@
         <v>20</v>
       </c>
       <c r="D165" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3166,7 +3160,7 @@
         <v>21</v>
       </c>
       <c r="D166" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/data/solution_finder_dataset.xlsx
+++ b/data/solution_finder_dataset.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$D$1:$D$166</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -70,9 +70,6 @@
     <t>Rough &amp; Bumpy Skin</t>
   </si>
   <si>
-    <t xml:space="preserve">Body Acne </t>
-  </si>
-  <si>
     <t>Dullness</t>
   </si>
   <si>
@@ -91,9 +88,6 @@
     <t>ingredient_preferences</t>
   </si>
   <si>
-    <t xml:space="preserve">Natural </t>
-  </si>
-  <si>
     <t>Organic</t>
   </si>
   <si>
@@ -413,6 +407,12 @@
   </si>
   <si>
     <t>Antipodes Baptise H2O Ultra Hydrating Water Gel</t>
+  </si>
+  <si>
+    <t>Body Zits</t>
+  </si>
+  <si>
+    <t>Natural</t>
   </si>
 </sst>
 </file>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -858,13 +858,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -872,13 +872,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -886,13 +886,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -900,13 +900,13 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -914,13 +914,13 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -928,13 +928,13 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -942,13 +942,13 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -956,13 +956,13 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -970,13 +970,13 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -984,13 +984,13 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -998,13 +998,13 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1012,13 +1012,13 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1026,13 +1026,13 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1040,13 +1040,13 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1054,13 +1054,13 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D16" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1068,13 +1068,13 @@
         <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1082,13 +1082,13 @@
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C18" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1096,13 +1096,13 @@
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D19" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1110,13 +1110,13 @@
         <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1124,13 +1124,13 @@
         <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D21" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1138,13 +1138,13 @@
         <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1152,13 +1152,13 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D23" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1166,13 +1166,13 @@
         <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D24" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1180,13 +1180,13 @@
         <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D25" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1194,13 +1194,13 @@
         <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C26" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D26" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1208,13 +1208,13 @@
         <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D27" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1222,13 +1222,13 @@
         <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C28" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D28" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1236,13 +1236,13 @@
         <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C29" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D29" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1250,13 +1250,13 @@
         <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C30" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D30" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1264,13 +1264,13 @@
         <v>2</v>
       </c>
       <c r="B31" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C31" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D31" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1278,13 +1278,13 @@
         <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C32" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D32" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1292,13 +1292,13 @@
         <v>3</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C33" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D33" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1306,13 +1306,13 @@
         <v>3</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C34" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D34" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1320,13 +1320,13 @@
         <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C35" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D35" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1334,13 +1334,13 @@
         <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C36" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D36" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1348,13 +1348,13 @@
         <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D37" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1362,13 +1362,13 @@
         <v>3</v>
       </c>
       <c r="B38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C38" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D38" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1376,13 +1376,13 @@
         <v>3</v>
       </c>
       <c r="B39" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C39" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D39" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1390,13 +1390,13 @@
         <v>3</v>
       </c>
       <c r="B40" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C40" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D40" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1404,13 +1404,13 @@
         <v>3</v>
       </c>
       <c r="B41" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D41" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1418,13 +1418,13 @@
         <v>3</v>
       </c>
       <c r="B42" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C42" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D42" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1432,13 +1432,13 @@
         <v>3</v>
       </c>
       <c r="B43" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C43" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D43" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1446,13 +1446,13 @@
         <v>3</v>
       </c>
       <c r="B44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C44" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D44" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1460,13 +1460,13 @@
         <v>3</v>
       </c>
       <c r="B45" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C45" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D45" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1474,13 +1474,13 @@
         <v>3</v>
       </c>
       <c r="B46" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C46" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D46" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1488,13 +1488,13 @@
         <v>4</v>
       </c>
       <c r="B47" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C47" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D47" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1502,13 +1502,13 @@
         <v>4</v>
       </c>
       <c r="B48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D48" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1516,13 +1516,13 @@
         <v>4</v>
       </c>
       <c r="B49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C49" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D49" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1530,13 +1530,13 @@
         <v>4</v>
       </c>
       <c r="B50" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C50" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D50" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1544,13 +1544,13 @@
         <v>4</v>
       </c>
       <c r="B51" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C51" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D51" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1558,13 +1558,13 @@
         <v>4</v>
       </c>
       <c r="B52" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C52" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D52" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1572,13 +1572,13 @@
         <v>4</v>
       </c>
       <c r="B53" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C53" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D53" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1586,13 +1586,13 @@
         <v>4</v>
       </c>
       <c r="B54" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D54" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1600,13 +1600,13 @@
         <v>4</v>
       </c>
       <c r="B55" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C55" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D55" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1614,13 +1614,13 @@
         <v>4</v>
       </c>
       <c r="B56" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C56" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D56" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1628,13 +1628,13 @@
         <v>4</v>
       </c>
       <c r="B57" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C57" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D57" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1642,13 +1642,13 @@
         <v>4</v>
       </c>
       <c r="B58" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C58" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D58" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1656,13 +1656,13 @@
         <v>4</v>
       </c>
       <c r="B59" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C59" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D59" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1670,13 +1670,13 @@
         <v>4</v>
       </c>
       <c r="B60" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C60" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D60" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1684,13 +1684,13 @@
         <v>4</v>
       </c>
       <c r="B61" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C61" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D61" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1698,13 +1698,13 @@
         <v>5</v>
       </c>
       <c r="B62" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C62" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D62" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1712,13 +1712,13 @@
         <v>5</v>
       </c>
       <c r="B63" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C63" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D63" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1726,13 +1726,13 @@
         <v>5</v>
       </c>
       <c r="B64" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C64" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D64" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1740,13 +1740,13 @@
         <v>5</v>
       </c>
       <c r="B65" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C65" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D65" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1754,13 +1754,13 @@
         <v>5</v>
       </c>
       <c r="B66" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C66" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D66" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1768,13 +1768,13 @@
         <v>5</v>
       </c>
       <c r="B67" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C67" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D67" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1782,13 +1782,13 @@
         <v>5</v>
       </c>
       <c r="B68" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C68" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D68" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1796,13 +1796,13 @@
         <v>5</v>
       </c>
       <c r="B69" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C69" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D69" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1810,13 +1810,13 @@
         <v>5</v>
       </c>
       <c r="B70" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C70" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D70" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1824,13 +1824,13 @@
         <v>5</v>
       </c>
       <c r="B71" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C71" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D71" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1838,13 +1838,13 @@
         <v>5</v>
       </c>
       <c r="B72" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C72" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D72" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1852,13 +1852,13 @@
         <v>5</v>
       </c>
       <c r="B73" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C73" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D73" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1866,13 +1866,13 @@
         <v>5</v>
       </c>
       <c r="B74" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C74" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D74" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -1880,13 +1880,13 @@
         <v>5</v>
       </c>
       <c r="B75" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C75" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D75" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1894,13 +1894,13 @@
         <v>5</v>
       </c>
       <c r="B76" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C76" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D76" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -1908,13 +1908,13 @@
         <v>6</v>
       </c>
       <c r="B77" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C77" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D77" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1922,13 +1922,13 @@
         <v>6</v>
       </c>
       <c r="B78" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C78" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D78" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1936,13 +1936,13 @@
         <v>6</v>
       </c>
       <c r="B79" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C79" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D79" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -1950,13 +1950,13 @@
         <v>6</v>
       </c>
       <c r="B80" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C80" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D80" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -1964,13 +1964,13 @@
         <v>6</v>
       </c>
       <c r="B81" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C81" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D81" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -1978,13 +1978,13 @@
         <v>6</v>
       </c>
       <c r="B82" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C82" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D82" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1992,13 +1992,13 @@
         <v>6</v>
       </c>
       <c r="B83" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C83" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D83" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2006,13 +2006,13 @@
         <v>6</v>
       </c>
       <c r="B84" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C84" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D84" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2020,13 +2020,13 @@
         <v>6</v>
       </c>
       <c r="B85" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C85" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D85" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2034,13 +2034,13 @@
         <v>6</v>
       </c>
       <c r="B86" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C86" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D86" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2048,13 +2048,13 @@
         <v>6</v>
       </c>
       <c r="B87" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C87" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D87" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2062,13 +2062,13 @@
         <v>6</v>
       </c>
       <c r="B88" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C88" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D88" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2076,13 +2076,13 @@
         <v>6</v>
       </c>
       <c r="B89" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C89" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D89" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2090,13 +2090,13 @@
         <v>6</v>
       </c>
       <c r="B90" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C90" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D90" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2104,13 +2104,13 @@
         <v>6</v>
       </c>
       <c r="B91" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C91" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D91" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2118,13 +2118,13 @@
         <v>7</v>
       </c>
       <c r="B92" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C92" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D92" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2132,13 +2132,13 @@
         <v>7</v>
       </c>
       <c r="B93" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C93" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D93" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2146,13 +2146,13 @@
         <v>7</v>
       </c>
       <c r="B94" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C94" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D94" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2160,13 +2160,13 @@
         <v>7</v>
       </c>
       <c r="B95" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C95" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D95" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2174,13 +2174,13 @@
         <v>7</v>
       </c>
       <c r="B96" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C96" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D96" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2188,13 +2188,13 @@
         <v>7</v>
       </c>
       <c r="B97" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C97" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D97" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2202,13 +2202,13 @@
         <v>7</v>
       </c>
       <c r="B98" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C98" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D98" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2216,13 +2216,13 @@
         <v>7</v>
       </c>
       <c r="B99" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C99" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D99" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2230,13 +2230,13 @@
         <v>7</v>
       </c>
       <c r="B100" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C100" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D100" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2244,13 +2244,13 @@
         <v>7</v>
       </c>
       <c r="B101" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C101" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D101" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2258,13 +2258,13 @@
         <v>7</v>
       </c>
       <c r="B102" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C102" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D102" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2272,13 +2272,13 @@
         <v>7</v>
       </c>
       <c r="B103" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C103" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D103" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2286,13 +2286,13 @@
         <v>7</v>
       </c>
       <c r="B104" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C104" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D104" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2300,13 +2300,13 @@
         <v>7</v>
       </c>
       <c r="B105" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C105" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D105" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="15">
@@ -2314,13 +2314,13 @@
         <v>7</v>
       </c>
       <c r="B106" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C106" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2328,13 +2328,13 @@
         <v>8</v>
       </c>
       <c r="B107" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C107" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D107" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2342,13 +2342,13 @@
         <v>8</v>
       </c>
       <c r="B108" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C108" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D108" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2356,13 +2356,13 @@
         <v>8</v>
       </c>
       <c r="B109" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C109" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D109" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2370,13 +2370,13 @@
         <v>8</v>
       </c>
       <c r="B110" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C110" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D110" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2384,13 +2384,13 @@
         <v>8</v>
       </c>
       <c r="B111" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C111" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D111" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2398,13 +2398,13 @@
         <v>8</v>
       </c>
       <c r="B112" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C112" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D112" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2412,13 +2412,13 @@
         <v>8</v>
       </c>
       <c r="B113" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C113" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D113" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2426,13 +2426,13 @@
         <v>8</v>
       </c>
       <c r="B114" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C114" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D114" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2440,13 +2440,13 @@
         <v>8</v>
       </c>
       <c r="B115" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C115" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D115" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2454,13 +2454,13 @@
         <v>8</v>
       </c>
       <c r="B116" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C116" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D116" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2468,13 +2468,13 @@
         <v>8</v>
       </c>
       <c r="B117" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C117" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D117" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2482,13 +2482,13 @@
         <v>8</v>
       </c>
       <c r="B118" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C118" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D118" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2496,13 +2496,13 @@
         <v>8</v>
       </c>
       <c r="B119" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C119" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D119" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2510,13 +2510,13 @@
         <v>8</v>
       </c>
       <c r="B120" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C120" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D120" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2524,13 +2524,13 @@
         <v>8</v>
       </c>
       <c r="B121" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C121" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D121" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2538,13 +2538,13 @@
         <v>9</v>
       </c>
       <c r="B122" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C122" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D122" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2552,13 +2552,13 @@
         <v>9</v>
       </c>
       <c r="B123" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C123" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D123" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2566,13 +2566,13 @@
         <v>9</v>
       </c>
       <c r="B124" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C124" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D124" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2580,13 +2580,13 @@
         <v>9</v>
       </c>
       <c r="B125" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C125" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D125" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2594,13 +2594,13 @@
         <v>9</v>
       </c>
       <c r="B126" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C126" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D126" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2608,13 +2608,13 @@
         <v>9</v>
       </c>
       <c r="B127" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C127" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2622,13 +2622,13 @@
         <v>9</v>
       </c>
       <c r="B128" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C128" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D128" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2636,13 +2636,13 @@
         <v>9</v>
       </c>
       <c r="B129" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C129" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D129" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2650,13 +2650,13 @@
         <v>9</v>
       </c>
       <c r="B130" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C130" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D130" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2664,13 +2664,13 @@
         <v>9</v>
       </c>
       <c r="B131" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C131" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D131" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2678,13 +2678,13 @@
         <v>9</v>
       </c>
       <c r="B132" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C132" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2692,13 +2692,13 @@
         <v>9</v>
       </c>
       <c r="B133" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C133" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D133" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2706,13 +2706,13 @@
         <v>9</v>
       </c>
       <c r="B134" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C134" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2720,13 +2720,13 @@
         <v>9</v>
       </c>
       <c r="B135" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C135" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D135" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2734,437 +2734,437 @@
         <v>9</v>
       </c>
       <c r="B136" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C136" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D136" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="B137" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C137" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D137" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="138" spans="1:4">
       <c r="A138" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="B138" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C138" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D138" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="B139" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C139" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D139" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="B140" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C140" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D140" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="B141" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C141" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D141" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="B142" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C142" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D142" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="143" spans="1:4">
       <c r="A143" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="B143" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C143" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D143" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="B144" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C144" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D144" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="B145" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C145" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D145" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="B146" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C146" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D146" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="B147" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C147" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="B148" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C148" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D148" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="B149" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C149" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D149" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="B150" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C150" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D150" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="B151" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C151" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D151" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B152" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C152" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D152" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B153" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C153" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D153" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="154" spans="1:4">
       <c r="A154" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B154" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C154" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D154" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B155" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C155" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D155" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B156" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C156" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D156" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B157" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C157" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D157" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="158" spans="1:4">
       <c r="A158" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B158" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C158" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D158" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="159" spans="1:4">
       <c r="A159" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B159" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C159" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D159" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B160" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C160" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D160" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="161" spans="1:4">
       <c r="A161" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B161" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C161" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D161" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="162" spans="1:4">
       <c r="A162" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B162" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C162" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D162" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B163" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C163" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D163" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B164" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C164" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D164" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B165" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C165" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D165" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B166" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C166" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D166" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A166"/>
+  <autoFilter ref="D1:D166"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
